--- a/12605501.xlsx
+++ b/12605501.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kunwar Khullar\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kunwar Khullar\Downloads\py\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{63D773AF-9798-4AA5-A87D-A9A1A8A3144D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796A97C9-229A-4A6E-8D2F-7E10521DAD59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -207,6 +207,21 @@
   <si>
     <t>August/September</t>
   </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Felt quite Exhausted</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Feeling Not well, due to cough and cold</t>
+  </si>
 </sst>
 </file>
 
@@ -344,7 +359,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -388,7 +403,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -867,7 +881,7 @@
     <col min="2" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="10" max="10" width="18.88671875" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="15" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
@@ -904,10 +918,10 @@
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="21">
         <v>12605501</v>
       </c>
-      <c r="G2" s="22"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -921,10 +935,10 @@
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="21"/>
+      <c r="G3" s="20"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
@@ -1035,65 +1049,117 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+      <c r="A7" s="13">
+        <v>46240</v>
+      </c>
+      <c r="B7" s="14">
+        <v>480</v>
+      </c>
+      <c r="C7" s="14">
+        <v>60</v>
+      </c>
+      <c r="D7" s="14">
+        <v>240</v>
+      </c>
+      <c r="E7" s="14">
+        <v>60</v>
+      </c>
+      <c r="F7" s="14">
+        <v>50</v>
+      </c>
+      <c r="G7" s="14">
+        <v>6</v>
+      </c>
+      <c r="H7" s="14">
+        <v>35</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>925</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+        <v>515</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="13">
+        <v>46241</v>
+      </c>
+      <c r="B8" s="14">
+        <v>440</v>
+      </c>
+      <c r="C8" s="14">
+        <v>60</v>
+      </c>
+      <c r="D8" s="14">
+        <v>280</v>
+      </c>
+      <c r="E8" s="14">
+        <v>60</v>
+      </c>
+      <c r="F8" s="14">
+        <v>50</v>
+      </c>
+      <c r="G8" s="14">
+        <v>5</v>
+      </c>
+      <c r="H8" s="14">
+        <v>45</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>935</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>505</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
+      <c r="A9" s="13">
+        <v>46242</v>
+      </c>
+      <c r="B9" s="14">
+        <v>480</v>
+      </c>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
       <c r="F9" s="14"/>
       <c r="G9" s="14"/>
       <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>480</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>960</v>
       </c>
       <c r="K9" s="16"/>
       <c r="L9" s="16"/>
@@ -1101,21 +1167,25 @@
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
+      <c r="A10" s="13">
+        <v>46243</v>
+      </c>
+      <c r="B10" s="14">
+        <v>480</v>
+      </c>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
       <c r="E10" s="14"/>
       <c r="F10" s="14"/>
       <c r="G10" s="14"/>
       <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>480</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>960</v>
       </c>
       <c r="K10" s="16"/>
       <c r="L10" s="16"/>
@@ -1123,21 +1193,25 @@
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
+      <c r="A11" s="13">
+        <v>46244</v>
+      </c>
+      <c r="B11" s="14">
+        <v>480</v>
+      </c>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
       <c r="F11" s="14"/>
       <c r="G11" s="14"/>
       <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>480</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>960</v>
       </c>
       <c r="K11" s="16"/>
       <c r="L11" s="16"/>
@@ -1145,21 +1219,25 @@
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
+      <c r="A12" s="13">
+        <v>46245</v>
+      </c>
+      <c r="B12" s="14">
+        <v>480</v>
+      </c>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="F12" s="14"/>
       <c r="G12" s="14"/>
       <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>480</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>960</v>
       </c>
       <c r="K12" s="16"/>
       <c r="L12" s="16"/>
@@ -1167,21 +1245,25 @@
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
+      <c r="A13" s="13">
+        <v>46246</v>
+      </c>
+      <c r="B13" s="14">
+        <v>480</v>
+      </c>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="14"/>
       <c r="G13" s="14"/>
       <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>480</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>960</v>
       </c>
       <c r="K13" s="16"/>
       <c r="L13" s="16"/>
@@ -1189,21 +1271,25 @@
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
+      <c r="A14" s="13">
+        <v>46247</v>
+      </c>
+      <c r="B14" s="14">
+        <v>480</v>
+      </c>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="14"/>
       <c r="G14" s="14"/>
       <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>480</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>960</v>
       </c>
       <c r="K14" s="16"/>
       <c r="L14" s="16"/>
